--- a/Most_Victories.xlsx
+++ b/Most_Victories.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasgwartz/Desktop/Job/Projects/Python/Masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D2D730-7CC4-9341-AFC7-7F6A694763D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243DB300-7FF0-C14E-9411-D12884469D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15900" xr2:uid="{DF0FA514-08AB-F746-80CB-0722B88E922F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="15900" xr2:uid="{DF0FA514-08AB-F746-80CB-0722B88E922F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Most_Victories.xlsx
+++ b/Most_Victories.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasgwartz/Desktop/Job/Projects/Python/Masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243DB300-7FF0-C14E-9411-D12884469D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF893359-110F-1242-8254-2B771A19E92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="15900" xr2:uid="{DF0FA514-08AB-F746-80CB-0722B88E922F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Golfer Name</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>Scottie Scheffler</t>
+  </si>
+  <si>
+    <t>Rory McIlroy</t>
   </si>
 </sst>
 </file>
@@ -447,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F705C0-90BE-8F41-A25B-96575F68ACBA}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
@@ -605,6 +608,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
